--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA52"/>
+  <dimension ref="A1:BA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.2263836870578444</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>386</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>329</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>401</v>
@@ -752,13 +752,13 @@
         <v>1.118152524167562</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7473002159827213</v>
+        <v>0.02159827213822894</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.159159159159159</v>
+        <v>0.02102102102102102</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.713541666666667</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
         <v>1.457700650759219</v>
@@ -801,13 +801,13 @@
         <v>0.2263836870578444</v>
       </c>
       <c r="J3" t="n">
-        <v>9.105263157894736</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="K3" t="n">
-        <v>10.1578947368421</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="L3" t="n">
-        <v>8.657894736842104</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="M3" t="n">
         <v>10.55263157894737</v>
@@ -882,13 +882,13 @@
         <v>1.118152524167562</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7473002159827213</v>
+        <v>0.02159827213822894</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.159159159159159</v>
+        <v>0.02102102102102102</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.713541666666667</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
         <v>1.457700650759219</v>
@@ -931,13 +931,13 @@
         <v>0.2222665602553871</v>
       </c>
       <c r="J4" t="n">
-        <v>383</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
-        <v>487</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>332</v>
+        <v>16</v>
       </c>
       <c r="M4" t="n">
         <v>428</v>
@@ -1012,13 +1012,13 @@
         <v>0.9940119760479041</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8308026030368764</v>
+        <v>0.02819956616052061</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.11441647597254</v>
+        <v>0.03661327231121281</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.794594594594595</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="AN4" t="n">
         <v>1.488120950323974</v>
@@ -1061,13 +1061,13 @@
         <v>0.2222665602553871</v>
       </c>
       <c r="J5" t="n">
-        <v>10.07894736842105</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="K5" t="n">
-        <v>12.81578947368421</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="L5" t="n">
-        <v>8.736842105263158</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="M5" t="n">
         <v>11.26315789473684</v>
@@ -1142,13 +1142,13 @@
         <v>0.9940119760479045</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8308026030368764</v>
+        <v>0.02819956616052061</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.11441647597254</v>
+        <v>0.03661327231121281</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.794594594594595</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="AN5" t="n">
         <v>1.488120950323974</v>
@@ -1486,16 +1486,16 @@
         <v>317</v>
       </c>
       <c r="U8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>104</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1011:56</t>
+          <t>497:54</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>5.154</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.116</v>
+        <v>0.235</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.032</v>
+        <v>0.064</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.061</v>
+        <v>0.125</v>
       </c>
       <c r="BA8" t="n">
         <v>0.028</v>
@@ -1639,7 +1639,7 @@
         <v>57</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R9" t="n">
         <v>48</v>
@@ -1651,16 +1651,16 @@
         <v>462</v>
       </c>
       <c r="U9" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>83</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1494:15</t>
+          <t>760:51</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>7.772</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.117</v>
+        <v>0.23</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.053</v>
+        <v>0.104</v>
       </c>
       <c r="BA9" t="n">
         <v>0.146</v>
@@ -1816,16 +1816,16 @@
         <v>444</v>
       </c>
       <c r="U10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>101</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1807:40</t>
+          <t>848:08</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>10.676</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.117</v>
+        <v>0.249</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.013</v>
+        <v>0.027</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.043</v>
+        <v>0.092</v>
       </c>
       <c r="BA10" t="n">
         <v>0.035</v>
@@ -1969,7 +1969,7 @@
         <v>78</v>
       </c>
       <c r="Q11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R11" t="n">
         <v>63</v>
@@ -1981,16 +1981,16 @@
         <v>727</v>
       </c>
       <c r="U11" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>176</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1930:38</t>
+          <t>1009:29</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>6</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.122</v>
+        <v>0.234</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.021</v>
+        <v>0.039</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.166</v>
       </c>
       <c r="BA11" t="n">
         <v>0.111</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>02:59</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.037</v>
+        <v>0.162</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>71:07</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>1.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.027</v>
+        <v>0.091</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.048</v>
+        <v>0.159</v>
       </c>
       <c r="BA13" t="n">
         <v>0.001</v>
@@ -2476,16 +2476,16 @@
         <v>22</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>6</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>126:02</t>
+          <t>56:02</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.067</v>
+        <v>0.15</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.045</v>
+        <v>0.101</v>
       </c>
       <c r="BA14" t="n">
         <v>0.005</v>
@@ -2641,16 +2641,16 @@
         <v>36</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>13</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>193:38</t>
+          <t>83:44</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>5.833</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.104</v>
+        <v>0.24</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.013</v>
+        <v>0.031</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.035</v>
+        <v>0.081</v>
       </c>
       <c r="BA15" t="n">
         <v>0.005</v>
@@ -2971,16 +2971,16 @@
         <v>46</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>12</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>234:31</t>
+          <t>105:16</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>6.25</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.059</v>
+        <v>0.13</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.116</v>
+        <v>0.258</v>
       </c>
       <c r="BA17" t="n">
         <v>0.004</v>
@@ -3136,16 +3136,16 @@
         <v>356</v>
       </c>
       <c r="U18" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>70</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2011:44</t>
+          <t>959:10</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>13.056</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.056</v>
+        <v>0.117</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.022</v>
+        <v>0.045</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.058</v>
+        <v>0.123</v>
       </c>
       <c r="BA18" t="n">
         <v>0.034</v>
@@ -3301,10 +3301,10 @@
         <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>180:45</t>
+          <t>81:26</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>7.333</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.067</v>
+        <v>0.15</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.021</v>
+        <v>0.047</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.038</v>
+        <v>0.083</v>
       </c>
       <c r="BA19" t="n">
         <v>0.002</v>
@@ -3466,16 +3466,16 @@
         <v>132</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>46</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>712:10</t>
+          <t>313:59</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>7.3</v>
       </c>
       <c r="AX20" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AY20" t="n">
         <v>0.057</v>
       </c>
-      <c r="AY20" t="n">
-        <v>0.025</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>0.052</v>
+        <v>0.119</v>
       </c>
       <c r="BA20" t="n">
         <v>0.008</v>
@@ -3631,16 +3631,16 @@
         <v>435</v>
       </c>
       <c r="U21" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
         <v>132</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1544:53</t>
+          <t>856:24</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>5.031</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.147</v>
+        <v>0.265</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.064</v>
+        <v>0.116</v>
       </c>
       <c r="BA21" t="n">
         <v>0.139</v>
@@ -3796,16 +3796,16 @@
         <v>186</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>27</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>1801:47</t>
+          <t>884:25</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,13 +3885,13 @@
         <v>20.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.046</v>
+        <v>0.094</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.021</v>
+        <v>0.042</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.046</v>
+        <v>0.095</v>
       </c>
       <c r="BA22" t="n">
         <v>0.039</v>
@@ -3961,16 +3961,16 @@
         <v>669</v>
       </c>
       <c r="U23" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>249</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1577:19</t>
+          <t>886:21</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.126</v>
+        <v>0.225</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.076</v>
+        <v>0.136</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.081</v>
+        <v>0.144</v>
       </c>
       <c r="BA23" t="n">
         <v>0.034</v>
@@ -4126,16 +4126,16 @@
         <v>53</v>
       </c>
       <c r="U24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>15</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>285:50</t>
+          <t>145:16</t>
         </is>
       </c>
       <c r="AO24" t="n">
@@ -4215,13 +4215,13 @@
         <v>14</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.107</v>
+        <v>0.211</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.013</v>
+        <v>0.026</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.044</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="BA24" t="n">
         <v>0.016</v>
@@ -4291,10 +4291,10 @@
         <v>47</v>
       </c>
       <c r="U25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>307:35</t>
+          <t>137:15</t>
         </is>
       </c>
       <c r="AO25" t="n">
@@ -4380,13 +4380,13 @@
         <v>8.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.189</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.012</v>
+        <v>0.028</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.189</v>
       </c>
       <c r="BA25" t="n">
         <v>0.007</v>
@@ -4560,163 +4560,163 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3353</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>884</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1472</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="T27" t="n">
-        <v>118</v>
+        <v>4058</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.454</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>842</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7650:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>30</v>
+        <v>3164.52</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.458</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>5.213</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
@@ -4725,44 +4725,44 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>3353</v>
+        <v>3243</v>
       </c>
       <c r="D28" t="n">
-        <v>884</v>
+        <v>845</v>
       </c>
       <c r="E28" t="n">
-        <v>1472</v>
+        <v>1504</v>
       </c>
       <c r="F28" t="n">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="G28" t="n">
-        <v>931</v>
+        <v>1002</v>
       </c>
       <c r="H28" t="n">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="I28" t="n">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="J28" t="n">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="K28" t="n">
-        <v>916</v>
+        <v>863</v>
       </c>
       <c r="L28" t="n">
-        <v>333</v>
+        <v>437</v>
       </c>
       <c r="M28" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N28" t="n">
         <v>215</v>
@@ -4771,76 +4771,76 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q28" t="n">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="R28" t="n">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="S28" t="n">
-        <v>785</v>
+        <v>742</v>
       </c>
       <c r="T28" t="n">
-        <v>4058</v>
+        <v>3817</v>
       </c>
       <c r="U28" t="n">
-        <v>346</v>
+        <v>13</v>
       </c>
       <c r="V28" t="n">
-        <v>386</v>
+        <v>16</v>
       </c>
       <c r="W28" t="n">
-        <v>329</v>
+        <v>16</v>
       </c>
       <c r="X28" t="n">
-        <v>192</v>
+        <v>7</v>
       </c>
       <c r="Y28" t="n">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="Z28" t="n">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.869</v>
+        <v>0.859</v>
       </c>
       <c r="AB28" t="n">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AC28" t="n">
-        <v>654</v>
+        <v>706</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.454</v>
+        <v>0.439</v>
       </c>
       <c r="AE28" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="AF28" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.514</v>
+        <v>0.318</v>
       </c>
       <c r="AH28" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AI28" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.427</v>
+        <v>0.314</v>
       </c>
       <c r="AK28" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AL28" t="n">
-        <v>842</v>
+        <v>916</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.367</v>
+        <v>0.333</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -4848,40 +4848,40 @@
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>3164.52</v>
+        <v>3270.84</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.584</v>
+        <v>0.536</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.62</v>
+        <v>0.577</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.06</v>
+        <v>0.991</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.458</v>
+        <v>1.488</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.213</v>
+        <v>5.413</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.67</v>
+        <v>6.901</v>
       </c>
       <c r="AX28" t="n">
         <v>0.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.056</v>
+        <v>0.065</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.135</v>
+        <v>0.144</v>
       </c>
       <c r="BA28" t="n">
         <v>0</v>
@@ -4890,910 +4890,910 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>38</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3243</v>
-      </c>
-      <c r="D29" t="n">
-        <v>845</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1504</v>
-      </c>
-      <c r="F29" t="n">
-        <v>332</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1002</v>
-      </c>
-      <c r="H29" t="n">
-        <v>557</v>
-      </c>
-      <c r="I29" t="n">
-        <v>686</v>
-      </c>
-      <c r="J29" t="n">
-        <v>689</v>
-      </c>
-      <c r="K29" t="n">
-        <v>863</v>
-      </c>
-      <c r="L29" t="n">
-        <v>437</v>
-      </c>
-      <c r="M29" t="n">
-        <v>231</v>
-      </c>
-      <c r="N29" t="n">
-        <v>215</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>463</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>428</v>
-      </c>
-      <c r="R29" t="n">
-        <v>682</v>
-      </c>
-      <c r="S29" t="n">
-        <v>742</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3817</v>
-      </c>
-      <c r="U29" t="n">
-        <v>383</v>
-      </c>
-      <c r="V29" t="n">
-        <v>487</v>
-      </c>
-      <c r="W29" t="n">
-        <v>332</v>
-      </c>
-      <c r="X29" t="n">
-        <v>185</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1050</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1223</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>310</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>706</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>132</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>86</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>305</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>916</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>7650:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>3270.84</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.488</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>5.413</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>6.901</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
+          <t>#0 J. MOTLEY (Per Game)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>36</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.611</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T30" t="n">
+        <v>317</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.889</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.139</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>6.719</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>5.154</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#0 J. MOTLEY (Per Game)</t>
+          <t>#1 C. JONES (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>9.657999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>2.389</v>
+        <v>2.158</v>
       </c>
       <c r="E31" t="n">
-        <v>3.611</v>
+        <v>4.184</v>
       </c>
       <c r="F31" t="n">
-        <v>0.556</v>
+        <v>1.395</v>
       </c>
       <c r="G31" t="n">
-        <v>1.083</v>
+        <v>3.263</v>
       </c>
       <c r="H31" t="n">
-        <v>1.556</v>
+        <v>1.158</v>
       </c>
       <c r="I31" t="n">
-        <v>2.139</v>
+        <v>1.342</v>
       </c>
       <c r="J31" t="n">
-        <v>0.889</v>
+        <v>4.211</v>
       </c>
       <c r="K31" t="n">
-        <v>1.528</v>
+        <v>1.842</v>
       </c>
       <c r="L31" t="n">
-        <v>0.694</v>
+        <v>0.158</v>
       </c>
       <c r="M31" t="n">
-        <v>0.25</v>
+        <v>0.921</v>
       </c>
       <c r="N31" t="n">
-        <v>0.389</v>
+        <v>0.211</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.083</v>
+        <v>1.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>1.342</v>
       </c>
       <c r="R31" t="n">
-        <v>1.778</v>
+        <v>1.263</v>
       </c>
       <c r="S31" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>317</v>
+        <v>462</v>
       </c>
       <c r="U31" t="n">
-        <v>0.5</v>
+        <v>0.079</v>
       </c>
       <c r="V31" t="n">
-        <v>1.194</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.722</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.889</v>
+        <v>2.184</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.139</v>
+        <v>2.658</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.92</v>
+        <v>0.822</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.944</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.75</v>
+        <v>1.947</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.54</v>
+        <v>0.419</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.111</v>
+        <v>0.316</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.278</v>
+        <v>0.737</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.4</v>
+        <v>0.429</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.083</v>
+        <v>0.079</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.083</v>
+        <v>0.184</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1</v>
+        <v>0.429</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.472</v>
+        <v>1.316</v>
       </c>
       <c r="AL31" t="n">
-        <v>1</v>
+        <v>3.079</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.472</v>
+        <v>0.427</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>28:06</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>6.719</v>
+        <v>9.538</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.71</v>
+        <v>0.601</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.191</v>
+        <v>1.013</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.161</v>
+        <v>0.157</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.331</v>
+        <v>0.155</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.821</v>
+        <v>2.807</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.333</v>
+        <v>4.965</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.154</v>
+        <v>7.772</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.116</v>
+        <v>0.23</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.032</v>
+        <v>0.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.061</v>
+        <v>0.104</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.03</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#1 C. JONES (Per Game)</t>
+          <t>#2 A. BLAKENEY (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>9.657999999999999</v>
+        <v>13.158</v>
       </c>
       <c r="D32" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.105</v>
+      </c>
+      <c r="F32" t="n">
         <v>2.158</v>
       </c>
-      <c r="E32" t="n">
-        <v>4.184</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.395</v>
-      </c>
       <c r="G32" t="n">
-        <v>3.263</v>
+        <v>5.316</v>
       </c>
       <c r="H32" t="n">
-        <v>1.158</v>
+        <v>2.105</v>
       </c>
       <c r="I32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.763</v>
+      </c>
+      <c r="T32" t="n">
+        <v>444</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.789</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.342</v>
       </c>
-      <c r="J32" t="n">
-        <v>4.211</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.842</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>462</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.184</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.658</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.947</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0.737</v>
-      </c>
       <c r="AG32" t="n">
-        <v>0.429</v>
+        <v>0.549</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.079</v>
+        <v>0.237</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.184</v>
+        <v>0.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.429</v>
+        <v>0.474</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.316</v>
+        <v>1.921</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.079</v>
+        <v>4.816</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.427</v>
+        <v>0.399</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>39:19</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>9.538</v>
+        <v>11.495</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.571</v>
+        <v>0.587</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.601</v>
+        <v>0.625</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.013</v>
+        <v>1.145</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.157</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.155</v>
+        <v>0.223</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.807</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.965</v>
+        <v>9.676</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.772</v>
+        <v>10.676</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.117</v>
+        <v>0.249</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.005</v>
+        <v>0.027</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.053</v>
+        <v>0.092</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.146</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#2 A. BLAKENEY (Per Game)</t>
+          <t>#3 E. BRYANT (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>13.158</v>
+        <v>15.941</v>
       </c>
       <c r="D33" t="n">
-        <v>2.289</v>
+        <v>4.441</v>
       </c>
       <c r="E33" t="n">
-        <v>4.105</v>
+        <v>7.265</v>
       </c>
       <c r="F33" t="n">
-        <v>2.158</v>
+        <v>1.206</v>
       </c>
       <c r="G33" t="n">
-        <v>5.316</v>
+        <v>3.118</v>
       </c>
       <c r="H33" t="n">
-        <v>2.105</v>
+        <v>3.441</v>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>3.853</v>
       </c>
       <c r="J33" t="n">
-        <v>0.974</v>
+        <v>3.382</v>
       </c>
       <c r="K33" t="n">
-        <v>1.816</v>
+        <v>4.353</v>
       </c>
       <c r="L33" t="n">
-        <v>0.474</v>
+        <v>0.912</v>
       </c>
       <c r="M33" t="n">
-        <v>0.368</v>
+        <v>0.706</v>
       </c>
       <c r="N33" t="n">
-        <v>0.763</v>
+        <v>0.441</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.974</v>
+        <v>2.294</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.895</v>
+        <v>2.147</v>
       </c>
       <c r="R33" t="n">
-        <v>1.289</v>
+        <v>1.853</v>
       </c>
       <c r="S33" t="n">
-        <v>1.763</v>
+        <v>4.941</v>
       </c>
       <c r="T33" t="n">
-        <v>444</v>
+        <v>727</v>
       </c>
       <c r="U33" t="n">
-        <v>1.579</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.132</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.447</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.658</v>
+        <v>5.176</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.789</v>
+        <v>5.853</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.953</v>
+        <v>0.884</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>2.235</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.079</v>
+        <v>4.235</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.481</v>
+        <v>0.528</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.737</v>
+        <v>0.471</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.342</v>
+        <v>0.618</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.549</v>
+        <v>0.762</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.237</v>
+        <v>0.118</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.5</v>
+        <v>0.265</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.474</v>
+        <v>0.444</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.921</v>
+        <v>1.088</v>
       </c>
       <c r="AL33" t="n">
-        <v>4.816</v>
+        <v>2.853</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.399</v>
+        <v>0.381</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>47:34</t>
+          <t>29:41</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>11.495</v>
+        <v>14.372</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.587</v>
+        <v>0.602</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.625</v>
+        <v>0.66</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.145</v>
+        <v>1.109</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.223</v>
+        <v>0.331</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>1.474</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.676</v>
+        <v>4.526</v>
       </c>
       <c r="AW33" t="n">
-        <v>10.676</v>
+        <v>6</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.117</v>
+        <v>0.234</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.013</v>
+        <v>0.039</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.043</v>
+        <v>0.166</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.035</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#3 E. BRYANT (Per Game)</t>
+          <t>#6 I. SEGEV (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>15.941</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>4.441</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>7.265</v>
+        <v>0.333</v>
       </c>
       <c r="F34" t="n">
-        <v>1.206</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.118</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.441</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3.853</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3.382</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>4.353</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.912</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.441</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.294</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.176</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.853</v>
+        <v>0.667</v>
       </c>
       <c r="S34" t="n">
-        <v>4.941</v>
+        <v>0.333</v>
       </c>
       <c r="T34" t="n">
-        <v>727</v>
+        <v>-2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.794</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.382</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.706</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.147</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>5.176</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.853</v>
+        <v>0.333</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.884</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.235</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.235</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.471</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.618</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.265</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.088</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.853</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.381</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>56:47</t>
+          <t>00:59</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>14.372</v>
+        <v>0.333</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.602</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.109</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.331</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.474</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.526</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.122</v>
+        <v>0.162</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#6 I. SEGEV (Per Game)</t>
+          <t>#9 G. PALATIN (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.333</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -5802,13 +5802,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5820,19 +5820,19 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="R35" t="n">
-        <v>0.667</v>
+        <v>0.286</v>
       </c>
       <c r="S35" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5874,13 +5874,13 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
@@ -5893,111 +5893,111 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>04:20</t>
+          <t>01:31</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.037</v>
+        <v>0.091</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#9 G. PALATIN (Per Game)</t>
+          <t>#10 B. TIMOR (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C36" t="n">
-        <v>0.214</v>
+        <v>0.833</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="E36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.417</v>
       </c>
       <c r="F36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="G36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="J36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="K36" t="n">
-        <v>0.214</v>
+        <v>0.208</v>
       </c>
       <c r="L36" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.143</v>
+        <v>0.083</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.143</v>
+        <v>0.083</v>
       </c>
       <c r="R36" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -6012,19 +6012,19 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6039,160 +6039,160 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>05:04</t>
+          <t>02:20</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>0.286</v>
+        <v>0.727</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.75</v>
+        <v>0.633</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.75</v>
+        <v>0.648</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.75</v>
+        <v>1.147</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.5</v>
+        <v>0.115</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AV36" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.027</v>
+        <v>0.15</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.048</v>
+        <v>0.101</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#10 B. TIMOR (Per Game)</t>
+          <t>#11 T. ENNIS (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C37" t="n">
-        <v>0.833</v>
+        <v>2.25</v>
       </c>
       <c r="D37" t="n">
-        <v>0.208</v>
+        <v>0.15</v>
       </c>
       <c r="E37" t="n">
-        <v>0.417</v>
+        <v>0.55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.125</v>
+        <v>0.45</v>
       </c>
       <c r="G37" t="n">
-        <v>0.208</v>
+        <v>0.9</v>
       </c>
       <c r="H37" t="n">
-        <v>0.042</v>
+        <v>0.6</v>
       </c>
       <c r="I37" t="n">
-        <v>0.042</v>
+        <v>0.75</v>
       </c>
       <c r="J37" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K37" t="n">
-        <v>0.208</v>
+        <v>0.3</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.208</v>
+        <v>0.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0.083</v>
+        <v>0.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.083</v>
+        <v>0.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.083</v>
+        <v>0.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0.333</v>
+        <v>0.75</v>
       </c>
       <c r="S37" t="n">
-        <v>0.042</v>
+        <v>0.65</v>
       </c>
       <c r="T37" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="U37" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.125</v>
+        <v>0.35</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6204,160 +6204,160 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AM37" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK37" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0.727</v>
+        <v>2.08</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.633</v>
+        <v>0.569</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.648</v>
+        <v>0.632</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.147</v>
+        <v>1.082</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.115</v>
+        <v>0.144</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.067</v>
+        <v>0.414</v>
       </c>
       <c r="AU37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>7.5</v>
+        <v>4.833</v>
       </c>
       <c r="AW37" t="n">
-        <v>10.5</v>
+        <v>5.833</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.067</v>
+        <v>0.24</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.045</v>
+        <v>0.081</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#11 T. ENNIS (Per Game)</t>
+          <t>#14 O. BLAYZER (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.8120000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6378,124 +6378,124 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.569</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.082</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.144</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.414</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.833</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.833</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#14 O. BLAYZER (Per Game)</t>
+          <t>#15 K. EDWARDS (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6507,19 +6507,19 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -6534,499 +6534,499 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.635</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.092</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#15 K. EDWARDS (Per Game)</t>
+          <t>#17 C. MALCOLM (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>3.1</v>
+        <v>6.921</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4</v>
+        <v>1.711</v>
       </c>
       <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.184</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="F40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K40" t="n">
-        <v>2.4</v>
+        <v>2.737</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1</v>
+        <v>0.895</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1</v>
+        <v>0.789</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5</v>
+        <v>0.632</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4</v>
+        <v>0.474</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4</v>
+        <v>0.421</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.658</v>
       </c>
       <c r="S40" t="n">
-        <v>0.9</v>
+        <v>1.316</v>
       </c>
       <c r="T40" t="n">
-        <v>46</v>
+        <v>356</v>
       </c>
       <c r="U40" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>1.842</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.4</v>
+        <v>2.158</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.857</v>
+        <v>0.854</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>0.553</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.4</v>
+        <v>1.342</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.2</v>
+        <v>0.105</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.3</v>
+        <v>0.237</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.3</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.7</v>
+        <v>1.947</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.429</v>
+        <v>0.419</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>25:14</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>2.84</v>
+        <v>6.086</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.575</v>
+        <v>0.596</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.635</v>
+        <v>0.617</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.092</v>
+        <v>1.137</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.141</v>
+        <v>0.078</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.4</v>
+        <v>0.142</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.25</v>
+        <v>2.111</v>
       </c>
       <c r="AV40" t="n">
-        <v>5</v>
+        <v>10.944</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.25</v>
+        <v>13.056</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.059</v>
+        <v>0.117</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.116</v>
+        <v>0.123</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#17 C. MALCOLM (Per Game)</t>
+          <t>#20 L. RANDOLPH (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>6.921</v>
+        <v>2.111</v>
       </c>
       <c r="D41" t="n">
-        <v>1.711</v>
+        <v>0.778</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>1.667</v>
       </c>
       <c r="F41" t="n">
-        <v>0.921</v>
+        <v>0.111</v>
       </c>
       <c r="G41" t="n">
-        <v>2.184</v>
+        <v>0.556</v>
       </c>
       <c r="H41" t="n">
-        <v>0.737</v>
+        <v>0.222</v>
       </c>
       <c r="I41" t="n">
-        <v>0.974</v>
+        <v>0.556</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0.222</v>
       </c>
       <c r="K41" t="n">
-        <v>2.737</v>
+        <v>0.667</v>
       </c>
       <c r="L41" t="n">
-        <v>0.895</v>
+        <v>0.333</v>
       </c>
       <c r="M41" t="n">
-        <v>0.789</v>
+        <v>0.222</v>
       </c>
       <c r="N41" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.474</v>
+        <v>0.333</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.421</v>
+        <v>0.333</v>
       </c>
       <c r="R41" t="n">
-        <v>1.658</v>
+        <v>1.444</v>
       </c>
       <c r="S41" t="n">
-        <v>1.316</v>
+        <v>0.778</v>
       </c>
       <c r="T41" t="n">
-        <v>356</v>
+        <v>8</v>
       </c>
       <c r="U41" t="n">
-        <v>0.974</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.237</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.842</v>
+        <v>0.333</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.158</v>
+        <v>0.444</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.854</v>
+        <v>0.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.553</v>
+        <v>0.222</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.342</v>
+        <v>0.889</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.412</v>
+        <v>0.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.053</v>
+        <v>0.444</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.237</v>
+        <v>0.556</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.222</v>
+        <v>0.8</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.237</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.947</v>
+        <v>0.556</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.419</v>
+        <v>0.2</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>52:56</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>6.086</v>
+        <v>2.8</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.596</v>
+        <v>0.425</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.617</v>
+        <v>0.428</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.137</v>
+        <v>0.754</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.078</v>
+        <v>0.119</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.142</v>
+        <v>0.1</v>
       </c>
       <c r="AU41" t="n">
-        <v>2.111</v>
+        <v>0.667</v>
       </c>
       <c r="AV41" t="n">
-        <v>10.944</v>
+        <v>6.667</v>
       </c>
       <c r="AW41" t="n">
-        <v>13.056</v>
+        <v>7.333</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.056</v>
+        <v>0.15</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.022</v>
+        <v>0.047</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.058</v>
+        <v>0.083</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.034</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#20 L. RANDOLPH (Per Game)</t>
+          <t>#21 T. ODIASE (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C42" t="n">
-        <v>2.111</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.778</v>
+        <v>1.212</v>
       </c>
       <c r="E42" t="n">
-        <v>1.667</v>
+        <v>1.909</v>
       </c>
       <c r="F42" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.222</v>
+        <v>0.576</v>
       </c>
       <c r="I42" t="n">
-        <v>0.556</v>
+        <v>0.758</v>
       </c>
       <c r="J42" t="n">
-        <v>0.222</v>
+        <v>0.303</v>
       </c>
       <c r="K42" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.333</v>
+        <v>0.424</v>
       </c>
       <c r="M42" t="n">
-        <v>0.222</v>
+        <v>0.303</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.333</v>
+        <v>0.303</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.333</v>
+        <v>0.303</v>
       </c>
       <c r="R42" t="n">
-        <v>1.444</v>
+        <v>1.121</v>
       </c>
       <c r="S42" t="n">
-        <v>0.778</v>
+        <v>0.879</v>
       </c>
       <c r="T42" t="n">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="U42" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.556</v>
+        <v>0.061</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.333</v>
+        <v>1.394</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.444</v>
+        <v>1.697</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.75</v>
+        <v>0.821</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.222</v>
+        <v>0.394</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.889</v>
+        <v>0.788</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
@@ -7038,952 +7038,952 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>2.8</v>
+        <v>2.545</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.425</v>
+        <v>0.635</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.428</v>
+        <v>0.669</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.754</v>
+        <v>1.179</v>
       </c>
       <c r="AS42" t="n">
         <v>0.119</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.1</v>
+        <v>0.302</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AV42" t="n">
-        <v>6.667</v>
+        <v>6.3</v>
       </c>
       <c r="AW42" t="n">
-        <v>7.333</v>
+        <v>7.3</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.067</v>
+        <v>0.129</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.021</v>
+        <v>0.057</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.038</v>
+        <v>0.119</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#21 T. ODIASE (Per Game)</t>
+          <t>#22 V. MICIC (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>11.389</v>
       </c>
       <c r="D43" t="n">
-        <v>1.212</v>
+        <v>2.222</v>
       </c>
       <c r="E43" t="n">
-        <v>1.909</v>
+        <v>4.111</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1.611</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>5.222</v>
       </c>
       <c r="H43" t="n">
-        <v>0.576</v>
+        <v>2.111</v>
       </c>
       <c r="I43" t="n">
-        <v>0.758</v>
+        <v>2.333</v>
       </c>
       <c r="J43" t="n">
-        <v>0.303</v>
+        <v>4.222</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>2.444</v>
       </c>
       <c r="L43" t="n">
-        <v>0.424</v>
+        <v>0.111</v>
       </c>
       <c r="M43" t="n">
-        <v>0.303</v>
+        <v>0.889</v>
       </c>
       <c r="N43" t="n">
-        <v>0.394</v>
+        <v>0.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.303</v>
+        <v>2.694</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.303</v>
+        <v>2.556</v>
       </c>
       <c r="R43" t="n">
-        <v>1.121</v>
+        <v>2.139</v>
       </c>
       <c r="S43" t="n">
-        <v>0.879</v>
+        <v>3.083</v>
       </c>
       <c r="T43" t="n">
-        <v>132</v>
+        <v>435</v>
       </c>
       <c r="U43" t="n">
-        <v>0.091</v>
+        <v>0.056</v>
       </c>
       <c r="V43" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.333</v>
+        <v>0.056</v>
       </c>
       <c r="X43" t="n">
-        <v>0.242</v>
+        <v>0.028</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.394</v>
+        <v>3.667</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.697</v>
+        <v>4.139</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.821</v>
+        <v>0.886</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.394</v>
+        <v>0.583</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.788</v>
+        <v>1.861</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.5</v>
+        <v>0.313</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AJ43" t="n">
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.611</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>5.139</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>23:47</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>2.545</v>
+        <v>13.054</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.635</v>
+        <v>0.497</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.669</v>
+        <v>0.55</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.179</v>
+        <v>0.872</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.119</v>
+        <v>0.206</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.302</v>
+        <v>0.226</v>
       </c>
       <c r="AU43" t="n">
-        <v>1</v>
+        <v>1.567</v>
       </c>
       <c r="AV43" t="n">
-        <v>6.3</v>
+        <v>3.464</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.3</v>
+        <v>5.031</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.057</v>
+        <v>0.265</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.052</v>
+        <v>0.116</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.01</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#22 V. MICIC (Per Game)</t>
+          <t>#24 I. WAINRIGHT (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C44" t="n">
-        <v>11.389</v>
+        <v>4.289</v>
       </c>
       <c r="D44" t="n">
-        <v>2.222</v>
+        <v>0.658</v>
       </c>
       <c r="E44" t="n">
-        <v>4.111</v>
+        <v>1.105</v>
       </c>
       <c r="F44" t="n">
-        <v>1.611</v>
+        <v>0.895</v>
       </c>
       <c r="G44" t="n">
-        <v>5.222</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>2.111</v>
+        <v>0.289</v>
       </c>
       <c r="I44" t="n">
-        <v>2.333</v>
+        <v>0.395</v>
       </c>
       <c r="J44" t="n">
-        <v>4.222</v>
+        <v>1.211</v>
       </c>
       <c r="K44" t="n">
-        <v>2.444</v>
+        <v>1.947</v>
       </c>
       <c r="L44" t="n">
-        <v>0.111</v>
+        <v>0.763</v>
       </c>
       <c r="M44" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5</v>
+        <v>0.184</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.694</v>
+        <v>0.263</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.556</v>
+        <v>0.158</v>
       </c>
       <c r="R44" t="n">
-        <v>2.139</v>
+        <v>2.553</v>
       </c>
       <c r="S44" t="n">
-        <v>3.083</v>
+        <v>1.105</v>
       </c>
       <c r="T44" t="n">
-        <v>435</v>
+        <v>186</v>
       </c>
       <c r="U44" t="n">
-        <v>1.694</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.472</v>
+        <v>0.079</v>
       </c>
       <c r="W44" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.667</v>
+        <v>0.711</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.139</v>
+        <v>0.842</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.886</v>
+        <v>0.844</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.583</v>
+        <v>0.184</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.861</v>
+        <v>0.421</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.313</v>
+        <v>0.438</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.083</v>
+        <v>0.053</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.222</v>
+        <v>0.132</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.083</v>
+        <v>0.842</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.611</v>
+        <v>0.632</v>
       </c>
       <c r="AL44" t="n">
-        <v>5.139</v>
+        <v>2.158</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.314</v>
+        <v>0.293</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>42:54</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>13.054</v>
+        <v>4.542</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.497</v>
+        <v>0.487</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.55</v>
+        <v>0.501</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.872</v>
+        <v>0.944</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.206</v>
+        <v>0.058</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.226</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.567</v>
+        <v>4.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.464</v>
+        <v>15.6</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.031</v>
+        <v>20.2</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.147</v>
+        <v>0.094</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.003</v>
+        <v>0.042</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.064</v>
+        <v>0.095</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.148</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#24 I. WAINRIGHT (Per Game)</t>
+          <t>#25 D. OTURU (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>38</v>
       </c>
       <c r="C45" t="n">
-        <v>4.289</v>
+        <v>13.395</v>
       </c>
       <c r="D45" t="n">
-        <v>0.658</v>
+        <v>5.763</v>
       </c>
       <c r="E45" t="n">
-        <v>1.105</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.868</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.816</v>
+      </c>
+      <c r="J45" t="n">
         <v>0.895</v>
       </c>
-      <c r="G45" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1.211</v>
-      </c>
       <c r="K45" t="n">
-        <v>1.947</v>
+        <v>2.974</v>
       </c>
       <c r="L45" t="n">
-        <v>0.763</v>
+        <v>2.474</v>
       </c>
       <c r="M45" t="n">
-        <v>0.868</v>
+        <v>0.5</v>
       </c>
       <c r="N45" t="n">
-        <v>0.184</v>
+        <v>1.868</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.263</v>
+        <v>1.5</v>
       </c>
       <c r="Q45" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.368</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="T45" t="n">
+        <v>669</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>6.553</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>7.789</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.158</v>
       </c>
-      <c r="R45" t="n">
-        <v>2.553</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="T45" t="n">
-        <v>186</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="Y45" t="n">
+      <c r="AG45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AO45" t="n">
+        <v>10.844</v>
+      </c>
+      <c r="AP45" t="n">
         <v>0.711</v>
       </c>
-      <c r="Z45" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.158</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>47:24</t>
-        </is>
-      </c>
-      <c r="AO45" t="n">
-        <v>4.542</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0.487</v>
-      </c>
       <c r="AQ45" t="n">
-        <v>0.501</v>
+        <v>0.717</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.944</v>
+        <v>1.235</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.058</v>
+        <v>0.138</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="AU45" t="n">
-        <v>4.6</v>
+        <v>0.596</v>
       </c>
       <c r="AV45" t="n">
-        <v>15.6</v>
+        <v>5.404</v>
       </c>
       <c r="AW45" t="n">
-        <v>20.2</v>
+        <v>6</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.046</v>
+        <v>0.225</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.021</v>
+        <v>0.136</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.046</v>
+        <v>0.144</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.039</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#25 D. OTURU (Per Game)</t>
+          <t>#26 Y. MADAR (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C46" t="n">
-        <v>13.395</v>
+        <v>1.92</v>
       </c>
       <c r="D46" t="n">
-        <v>5.763</v>
+        <v>0.44</v>
       </c>
       <c r="E46" t="n">
-        <v>8.079000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T46" t="n">
+        <v>53</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="AO46" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AY46" t="n">
         <v>0.026</v>
       </c>
-      <c r="H46" t="n">
-        <v>1.868</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.816</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.974</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2.474</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1.868</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.447</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.658</v>
-      </c>
-      <c r="T46" t="n">
-        <v>669</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.026</v>
-      </c>
-      <c r="V46" t="n">
-        <v>3.053</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.579</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>6.553</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>7.789</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>41:30</t>
-        </is>
-      </c>
-      <c r="AO46" t="n">
-        <v>10.844</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>5.404</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0.076</v>
-      </c>
       <c r="AZ46" t="n">
-        <v>0.081</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#26 Y. MADAR (Per Game)</t>
+          <t>#41 T. GINAT (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C47" t="n">
-        <v>1.92</v>
+        <v>2.421</v>
       </c>
       <c r="D47" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.04</v>
+        <v>1.684</v>
       </c>
       <c r="F47" t="n">
-        <v>0.16</v>
+        <v>0.053</v>
       </c>
       <c r="G47" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="T47" t="n">
+        <v>47</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="T47" t="n">
-        <v>53</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AH47" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.12</v>
+        <v>0.053</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.96</v>
+        <v>0.526</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>2.539</v>
+        <v>2.827</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.333</v>
+        <v>0.488</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.41</v>
+        <v>0.482</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.756</v>
+        <v>0.856</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.079</v>
+        <v>0.112</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.275</v>
+        <v>0.119</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="AV47" t="n">
-        <v>10.2</v>
+        <v>7</v>
       </c>
       <c r="AW47" t="n">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.107</v>
+        <v>0.189</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.013</v>
+        <v>0.028</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.044</v>
+        <v>0.189</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#41 T. GINAT (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C48" t="n">
-        <v>2.421</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="L48" t="n">
         <v>1.684</v>
       </c>
-      <c r="F48" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1.211</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.158</v>
-      </c>
       <c r="M48" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.316</v>
+        <v>0.789</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -7992,31 +7992,31 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.947</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.8179999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
@@ -8028,219 +8028,219 @@
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>2.827</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.488</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.482</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.856</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.119</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>38</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>88.23699999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>23.263</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>38.737</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>9.132</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>14.316</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>17.974</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>17.684</v>
       </c>
       <c r="K49" t="n">
-        <v>2.211</v>
+        <v>24.105</v>
       </c>
       <c r="L49" t="n">
-        <v>1.684</v>
+        <v>8.763</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>6.053</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.658</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.789</v>
+        <v>12.132</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>10.553</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>17.737</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>20.658</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>4058</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>27.763</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>31.947</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>7.816</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>17.211</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.454</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>3.895</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>2.342</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>8.132</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>22.158</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>83.277</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.458</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>5.213</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="BA49" t="n">
         <v>0</v>
@@ -8249,495 +8249,165 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>38</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>85.342</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>22.237</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>39.579</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>8.737</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>26.368</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>14.658</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>18.053</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>18.132</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>22.711</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>6.079</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.658</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>12.184</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>11.263</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>17.947</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>19.526</v>
       </c>
       <c r="T50" t="n">
-        <v>118</v>
+        <v>3817</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>27.632</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>32.184</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>8.157999999999999</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>18.579</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>3.474</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>2.263</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>8.026</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>24.105</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>0.789</v>
+        <v>86.075</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>0.991</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.488</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>5.413</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>6.901</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>38</v>
-      </c>
-      <c r="C51" t="n">
-        <v>88.23699999999999</v>
-      </c>
-      <c r="D51" t="n">
-        <v>23.263</v>
-      </c>
-      <c r="E51" t="n">
-        <v>38.737</v>
-      </c>
-      <c r="F51" t="n">
-        <v>9.132</v>
-      </c>
-      <c r="G51" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>14.316</v>
-      </c>
-      <c r="I51" t="n">
-        <v>17.974</v>
-      </c>
-      <c r="J51" t="n">
-        <v>17.684</v>
-      </c>
-      <c r="K51" t="n">
-        <v>24.105</v>
-      </c>
-      <c r="L51" t="n">
-        <v>8.763</v>
-      </c>
-      <c r="M51" t="n">
-        <v>6.053</v>
-      </c>
-      <c r="N51" t="n">
-        <v>5.658</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>12.132</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>10.553</v>
-      </c>
-      <c r="R51" t="n">
-        <v>17.737</v>
-      </c>
-      <c r="S51" t="n">
-        <v>20.658</v>
-      </c>
-      <c r="T51" t="n">
-        <v>4058</v>
-      </c>
-      <c r="U51" t="n">
-        <v>9.105</v>
-      </c>
-      <c r="V51" t="n">
-        <v>10.158</v>
-      </c>
-      <c r="W51" t="n">
-        <v>8.657999999999999</v>
-      </c>
-      <c r="X51" t="n">
-        <v>5.053</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>27.763</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>31.947</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>17.211</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.454</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>3.895</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>8.132</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>22.158</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>83.277</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.458</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>5.213</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>38</v>
-      </c>
-      <c r="C52" t="n">
-        <v>85.342</v>
-      </c>
-      <c r="D52" t="n">
-        <v>22.237</v>
-      </c>
-      <c r="E52" t="n">
-        <v>39.579</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8.737</v>
-      </c>
-      <c r="G52" t="n">
-        <v>26.368</v>
-      </c>
-      <c r="H52" t="n">
-        <v>14.658</v>
-      </c>
-      <c r="I52" t="n">
-        <v>18.053</v>
-      </c>
-      <c r="J52" t="n">
-        <v>18.132</v>
-      </c>
-      <c r="K52" t="n">
-        <v>22.711</v>
-      </c>
-      <c r="L52" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M52" t="n">
-        <v>6.079</v>
-      </c>
-      <c r="N52" t="n">
-        <v>5.658</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>12.184</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>11.263</v>
-      </c>
-      <c r="R52" t="n">
-        <v>17.947</v>
-      </c>
-      <c r="S52" t="n">
-        <v>19.526</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3817</v>
-      </c>
-      <c r="U52" t="n">
-        <v>10.079</v>
-      </c>
-      <c r="V52" t="n">
-        <v>12.816</v>
-      </c>
-      <c r="W52" t="n">
-        <v>8.737</v>
-      </c>
-      <c r="X52" t="n">
-        <v>4.868</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>27.632</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>32.184</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>8.157999999999999</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>18.579</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>3.474</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>2.263</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>8.026</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>24.105</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>86.075</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.488</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>5.413</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>6.901</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="BA52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
@@ -671,13 +671,13 @@
         <v>0.2263836870578444</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>340</v>
       </c>
       <c r="M2" t="n">
         <v>401</v>
@@ -752,13 +752,13 @@
         <v>1.118152524167562</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02159827213822894</v>
+        <v>0.7710583153347732</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02102102102102102</v>
+        <v>1.174174174174174</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>1.67487684729064</v>
       </c>
       <c r="AN2" t="n">
         <v>1.457700650759219</v>
@@ -801,13 +801,13 @@
         <v>0.2263836870578444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2631578947368421</v>
+        <v>9.394736842105264</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1842105263157895</v>
+        <v>10.28947368421053</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1052631578947368</v>
+        <v>8.947368421052632</v>
       </c>
       <c r="M3" t="n">
         <v>10.55263157894737</v>
@@ -882,13 +882,13 @@
         <v>1.118152524167562</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02159827213822894</v>
+        <v>0.7710583153347733</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.02102102102102102</v>
+        <v>1.174174174174174</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>1.674876847290641</v>
       </c>
       <c r="AN3" t="n">
         <v>1.457700650759219</v>
@@ -931,13 +931,13 @@
         <v>0.2222665602553871</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>386</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>494</v>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>345</v>
       </c>
       <c r="M4" t="n">
         <v>428</v>
@@ -1012,13 +1012,13 @@
         <v>0.9940119760479041</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02819956616052061</v>
+        <v>0.8373101952277657</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03661327231121281</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.285714285714286</v>
+        <v>1.742424242424242</v>
       </c>
       <c r="AN4" t="n">
         <v>1.488120950323974</v>
@@ -1061,13 +1061,13 @@
         <v>0.2222665602553871</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3421052631578947</v>
+        <v>10.1578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4210526315789473</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4210526315789473</v>
+        <v>9.078947368421053</v>
       </c>
       <c r="M5" t="n">
         <v>11.26315789473684</v>
@@ -1142,13 +1142,13 @@
         <v>0.9940119760479045</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02819956616052061</v>
+        <v>0.8373101952277656</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03661327231121281</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.285714285714286</v>
+        <v>1.742424242424243</v>
       </c>
       <c r="AN5" t="n">
         <v>1.488120950323974</v>
@@ -1486,16 +1486,16 @@
         <v>317</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
         <v>104</v>
@@ -1651,16 +1651,16 @@
         <v>462</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y9" t="n">
         <v>83</v>
@@ -1816,16 +1816,16 @@
         <v>444</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="n">
         <v>101</v>
@@ -1981,16 +1981,16 @@
         <v>727</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y11" t="n">
         <v>176</v>
@@ -2476,16 +2476,16 @@
         <v>22</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
         <v>6</v>
@@ -2641,16 +2641,16 @@
         <v>36</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
         <v>13</v>
@@ -2971,16 +2971,16 @@
         <v>46</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
         <v>12</v>
@@ -3136,16 +3136,16 @@
         <v>356</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
         <v>70</v>
@@ -3301,10 +3301,10 @@
         <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3466,16 +3466,16 @@
         <v>132</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="n">
         <v>46</v>
@@ -3631,16 +3631,16 @@
         <v>435</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
         <v>132</v>
@@ -3796,16 +3796,16 @@
         <v>186</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
         <v>27</v>
@@ -3961,16 +3961,16 @@
         <v>669</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Y23" t="n">
         <v>249</v>
@@ -4126,16 +4126,16 @@
         <v>53</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="n">
         <v>15</v>
@@ -4291,10 +4291,10 @@
         <v>47</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>4058</v>
       </c>
       <c r="U27" t="n">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="W27" t="n">
-        <v>4</v>
+        <v>340</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="Y27" t="n">
         <v>1055</v>
@@ -4786,16 +4786,16 @@
         <v>3817</v>
       </c>
       <c r="U28" t="n">
-        <v>13</v>
+        <v>386</v>
       </c>
       <c r="V28" t="n">
-        <v>16</v>
+        <v>494</v>
       </c>
       <c r="W28" t="n">
-        <v>16</v>
+        <v>345</v>
       </c>
       <c r="X28" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="Y28" t="n">
         <v>1050</v>
@@ -5010,16 +5010,16 @@
         <v>317</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.111</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.472</v>
       </c>
       <c r="Y30" t="n">
         <v>2.889</v>
@@ -5175,16 +5175,16 @@
         <v>462</v>
       </c>
       <c r="U31" t="n">
-        <v>0.079</v>
+        <v>0.921</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.079</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="Y31" t="n">
         <v>2.184</v>
@@ -5340,16 +5340,16 @@
         <v>444</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.684</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.289</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="Y32" t="n">
         <v>2.658</v>
@@ -5505,16 +5505,16 @@
         <v>727</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.824</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.382</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.794</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.235</v>
       </c>
       <c r="Y33" t="n">
         <v>5.176</v>
@@ -6000,16 +6000,16 @@
         <v>22</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="Y36" t="n">
         <v>0.25</v>
@@ -6165,16 +6165,16 @@
         <v>36</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="Y37" t="n">
         <v>0.65</v>
@@ -6495,16 +6495,16 @@
         <v>46</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y39" t="n">
         <v>1.2</v>
@@ -6660,16 +6660,16 @@
         <v>356</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>0.974</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.289</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="Y40" t="n">
         <v>1.842</v>
@@ -6825,10 +6825,10 @@
         <v>8</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -6990,16 +6990,16 @@
         <v>132</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="V42" t="n">
-        <v>0.061</v>
+        <v>0.455</v>
       </c>
       <c r="W42" t="n">
-        <v>0.061</v>
+        <v>0.364</v>
       </c>
       <c r="X42" t="n">
-        <v>0.03</v>
+        <v>0.273</v>
       </c>
       <c r="Y42" t="n">
         <v>1.394</v>
@@ -7155,16 +7155,16 @@
         <v>435</v>
       </c>
       <c r="U43" t="n">
-        <v>0.056</v>
+        <v>1.694</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.472</v>
       </c>
       <c r="W43" t="n">
-        <v>0.056</v>
+        <v>1.194</v>
       </c>
       <c r="X43" t="n">
-        <v>0.028</v>
+        <v>0.694</v>
       </c>
       <c r="Y43" t="n">
         <v>3.667</v>
@@ -7320,16 +7320,16 @@
         <v>186</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="V44" t="n">
-        <v>0.079</v>
+        <v>0.868</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="Y44" t="n">
         <v>0.711</v>
@@ -7485,16 +7485,16 @@
         <v>669</v>
       </c>
       <c r="U45" t="n">
-        <v>0.053</v>
+        <v>1.026</v>
       </c>
       <c r="V45" t="n">
-        <v>0.053</v>
+        <v>3.105</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.553</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="Y45" t="n">
         <v>6.553</v>
@@ -7650,16 +7650,16 @@
         <v>53</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="Y46" t="n">
         <v>0.6</v>
@@ -7815,10 +7815,10 @@
         <v>47</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -8145,16 +8145,16 @@
         <v>4058</v>
       </c>
       <c r="U49" t="n">
-        <v>0.263</v>
+        <v>9.395</v>
       </c>
       <c r="V49" t="n">
-        <v>0.184</v>
+        <v>10.289</v>
       </c>
       <c r="W49" t="n">
-        <v>0.105</v>
+        <v>8.946999999999999</v>
       </c>
       <c r="X49" t="n">
-        <v>0.053</v>
+        <v>5.342</v>
       </c>
       <c r="Y49" t="n">
         <v>27.763</v>
@@ -8310,16 +8310,16 @@
         <v>3817</v>
       </c>
       <c r="U50" t="n">
-        <v>0.342</v>
+        <v>10.158</v>
       </c>
       <c r="V50" t="n">
-        <v>0.421</v>
+        <v>13</v>
       </c>
       <c r="W50" t="n">
-        <v>0.421</v>
+        <v>9.079000000000001</v>
       </c>
       <c r="X50" t="n">
-        <v>0.184</v>
+        <v>5.211</v>
       </c>
       <c r="Y50" t="n">
         <v>27.632</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_HAPOEL IBI TEL AVIV.xlsx
@@ -683,13 +683,13 @@
         <v>401</v>
       </c>
       <c r="N2" t="n">
-        <v>1055</v>
+        <v>511</v>
       </c>
       <c r="O2" t="n">
-        <v>1214</v>
+        <v>670</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5052018310445276</v>
+        <v>0.2788181439866833</v>
       </c>
       <c r="Q2" t="n">
         <v>297</v>
@@ -710,25 +710,25 @@
         <v>0.06158967956720766</v>
       </c>
       <c r="W2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="X2" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.04286308780690803</v>
       </c>
       <c r="Z2" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AA2" t="n">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3503953391593841</v>
+        <v>0.3445692883895131</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8690280065897859</v>
+        <v>0.7626865671641792</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4541284403669725</v>
@@ -737,13 +737,13 @@
         <v>0.5135135135135135</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4269662921348314</v>
+        <v>0.4271844660194175</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3669833729216152</v>
+        <v>0.3659420289855073</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.738056013179572</v>
+        <v>1.525373134328358</v>
       </c>
       <c r="AI2" t="n">
         <v>1.027027027027027</v>
@@ -813,13 +813,13 @@
         <v>10.55263157894737</v>
       </c>
       <c r="N3" t="n">
-        <v>27.76315789473684</v>
+        <v>13.44736842105263</v>
       </c>
       <c r="O3" t="n">
-        <v>31.94736842105263</v>
+        <v>17.63157894736842</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5052018310445276</v>
+        <v>0.2788181439866833</v>
       </c>
       <c r="Q3" t="n">
         <v>7.815789473684211</v>
@@ -840,25 +840,25 @@
         <v>0.06158967956720766</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="X3" t="n">
-        <v>2.342105263157895</v>
+        <v>2.710526315789474</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.04286308780690803</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.131578947368421</v>
+        <v>7.973684210526316</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.15789473684211</v>
+        <v>21.78947368421053</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3503953391593841</v>
+        <v>0.3445692883895131</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8690280065897859</v>
+        <v>0.7626865671641792</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4541284403669725</v>
@@ -867,13 +867,13 @@
         <v>0.5135135135135135</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4269662921348314</v>
+        <v>0.4271844660194175</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3669833729216152</v>
+        <v>0.3659420289855073</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.738056013179572</v>
+        <v>1.525373134328358</v>
       </c>
       <c r="AI3" t="n">
         <v>1.027027027027027</v>
@@ -943,13 +943,13 @@
         <v>428</v>
       </c>
       <c r="N4" t="n">
-        <v>1050</v>
+        <v>493</v>
       </c>
       <c r="O4" t="n">
-        <v>1223</v>
+        <v>666</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4880287310454908</v>
+        <v>0.2657621707901037</v>
       </c>
       <c r="Q4" t="n">
         <v>310</v>
@@ -970,25 +970,25 @@
         <v>0.05267358339984039</v>
       </c>
       <c r="W4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03431763766959298</v>
+        <v>0.03790901835594573</v>
       </c>
       <c r="Z4" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AA4" t="n">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3655227454110136</v>
+        <v>0.3619313647246608</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8585445625511039</v>
+        <v>0.7402402402402403</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4390934844192634</v>
@@ -997,13 +997,13 @@
         <v>0.3181818181818182</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.313953488372093</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3329694323144105</v>
+        <v>0.3318632855567806</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.717089125102208</v>
+        <v>1.480480480480481</v>
       </c>
       <c r="AI4" t="n">
         <v>0.6363636363636364</v>
@@ -1073,13 +1073,13 @@
         <v>11.26315789473684</v>
       </c>
       <c r="N5" t="n">
-        <v>27.63157894736842</v>
+        <v>12.97368421052632</v>
       </c>
       <c r="O5" t="n">
-        <v>32.18421052631579</v>
+        <v>17.52631578947368</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4880287310454908</v>
+        <v>0.2657621707901038</v>
       </c>
       <c r="Q5" t="n">
         <v>8.157894736842104</v>
@@ -1100,25 +1100,25 @@
         <v>0.05267358339984039</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="X5" t="n">
-        <v>2.263157894736842</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03431763766959298</v>
+        <v>0.03790901835594573</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.026315789473685</v>
+        <v>7.921052631578948</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.10526315789474</v>
+        <v>23.86842105263158</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3655227454110136</v>
+        <v>0.3619313647246608</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8585445625511039</v>
+        <v>0.7402402402402402</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4390934844192634</v>
@@ -1127,19 +1127,19 @@
         <v>0.3181818181818182</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.313953488372093</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3329694323144105</v>
+        <v>0.3318632855567806</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.717089125102208</v>
+        <v>1.48048048048048</v>
       </c>
       <c r="AI5" t="n">
         <v>0.6363636363636364</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9940119760479045</v>
+        <v>0.9940119760479041</v>
       </c>
       <c r="AK5" t="n">
         <v>0.8373101952277656</v>
@@ -1498,13 +1498,13 @@
         <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="Z8" t="n">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.92</v>
+        <v>0.842</v>
       </c>
       <c r="AB8" t="n">
         <v>34</v>
@@ -1663,13 +1663,13 @@
         <v>28</v>
       </c>
       <c r="Y9" t="n">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="Z9" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.822</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB9" t="n">
         <v>31</v>
@@ -1690,22 +1690,22 @@
         <v>0.429</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AL9" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>8</v>
       </c>
       <c r="Y10" t="n">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.953</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="AB10" t="n">
         <v>38</v>
@@ -1858,19 +1858,19 @@
         <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.474</v>
+        <v>0.391</v>
       </c>
       <c r="AK10" t="n">
         <v>73</v>
       </c>
       <c r="AL10" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.399</v>
+        <v>0.408</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="Z11" t="n">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.884</v>
+        <v>0.72</v>
       </c>
       <c r="AB11" t="n">
         <v>76</v>
@@ -2488,13 +2488,13 @@
         <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2653,13 +2653,13 @@
         <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AB15" t="n">
         <v>2</v>
@@ -2680,22 +2680,22 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3010,22 +3010,22 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK17" t="n">
         <v>2</v>
       </c>
-      <c r="AI17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>3</v>
-      </c>
       <c r="AL17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="Z18" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.854</v>
+        <v>0.778</v>
       </c>
       <c r="AB18" t="n">
         <v>21</v>
@@ -3175,22 +3175,22 @@
         <v>0.222</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.419</v>
+        <v>0.408</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
@@ -3313,13 +3313,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AB19" t="n">
         <v>2</v>
@@ -3478,13 +3478,13 @@
         <v>9</v>
       </c>
       <c r="Y20" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="Z20" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.821</v>
+        <v>0.73</v>
       </c>
       <c r="AB20" t="n">
         <v>13</v>
@@ -3643,13 +3643,13 @@
         <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="Z21" t="n">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.886</v>
+        <v>0.767</v>
       </c>
       <c r="AB21" t="n">
         <v>21</v>
@@ -3808,13 +3808,13 @@
         <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.844</v>
+        <v>0.762</v>
       </c>
       <c r="AB22" t="n">
         <v>7</v>
@@ -3835,22 +3835,22 @@
         <v>0.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.312</v>
+        <v>0.314</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.293</v>
+        <v>0.291</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>33</v>
       </c>
       <c r="Y23" t="n">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="Z23" t="n">
-        <v>296</v>
+        <v>225</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.841</v>
+        <v>0.791</v>
       </c>
       <c r="AB23" t="n">
         <v>38</v>
@@ -4138,10 +4138,10 @@
         <v>4</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
         <v>1</v>
@@ -4303,13 +4303,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="AB25" t="n">
         <v>5</v>
@@ -4633,13 +4633,13 @@
         <v>203</v>
       </c>
       <c r="Y27" t="n">
-        <v>1055</v>
+        <v>511</v>
       </c>
       <c r="Z27" t="n">
-        <v>1214</v>
+        <v>670</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.869</v>
+        <v>0.763</v>
       </c>
       <c r="AB27" t="n">
         <v>297</v>
@@ -4660,22 +4660,22 @@
         <v>0.514</v>
       </c>
       <c r="AH27" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AI27" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="AJ27" t="n">
         <v>0.427</v>
       </c>
       <c r="AK27" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AL27" t="n">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4798,13 +4798,13 @@
         <v>198</v>
       </c>
       <c r="Y28" t="n">
-        <v>1050</v>
+        <v>493</v>
       </c>
       <c r="Z28" t="n">
-        <v>1223</v>
+        <v>666</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.859</v>
+        <v>0.74</v>
       </c>
       <c r="AB28" t="n">
         <v>310</v>
@@ -4825,22 +4825,22 @@
         <v>0.318</v>
       </c>
       <c r="AH28" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AI28" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.314</v>
+        <v>0.326</v>
       </c>
       <c r="AK28" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AL28" t="n">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -5022,13 +5022,13 @@
         <v>0.472</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.889</v>
+        <v>1.333</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.139</v>
+        <v>1.583</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.92</v>
+        <v>0.842</v>
       </c>
       <c r="AB30" t="n">
         <v>0.944</v>
@@ -5187,13 +5187,13 @@
         <v>0.737</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.184</v>
+        <v>1.026</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.658</v>
+        <v>1.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.822</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB31" t="n">
         <v>0.8159999999999999</v>
@@ -5214,22 +5214,22 @@
         <v>0.429</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.079</v>
+        <v>0.105</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.184</v>
+        <v>0.237</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.316</v>
+        <v>1.289</v>
       </c>
       <c r="AL31" t="n">
-        <v>3.079</v>
+        <v>3.026</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.211</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.658</v>
+        <v>0.553</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.789</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.953</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="AB32" t="n">
         <v>1</v>
@@ -5382,19 +5382,19 @@
         <v>0.237</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.5</v>
+        <v>0.605</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.474</v>
+        <v>0.391</v>
       </c>
       <c r="AK32" t="n">
         <v>1.921</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.816</v>
+        <v>4.711</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.399</v>
+        <v>0.408</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>1.235</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.176</v>
+        <v>1.735</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.853</v>
+        <v>2.412</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.884</v>
+        <v>0.72</v>
       </c>
       <c r="AB33" t="n">
         <v>2.235</v>
@@ -6012,13 +6012,13 @@
         <v>0.083</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.25</v>
+        <v>0.208</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.333</v>
+        <v>0.292</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         <v>0.15</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.65</v>
+        <v>0.05</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AB37" t="n">
         <v>0.1</v>
@@ -6204,22 +6204,22 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6507,13 +6507,13 @@
         <v>0.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6534,22 +6534,22 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.2</v>
       </c>
-      <c r="AI39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0.3</v>
-      </c>
       <c r="AL39" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6672,13 +6672,13 @@
         <v>0.605</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.842</v>
+        <v>1.105</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.158</v>
+        <v>1.421</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.854</v>
+        <v>0.778</v>
       </c>
       <c r="AB40" t="n">
         <v>0.553</v>
@@ -6699,22 +6699,22 @@
         <v>0.222</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.105</v>
+        <v>0.158</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.237</v>
+        <v>0.316</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.947</v>
+        <v>1.868</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.419</v>
+        <v>0.408</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.333</v>
+        <v>0.111</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AB41" t="n">
         <v>0.222</v>
@@ -7002,13 +7002,13 @@
         <v>0.273</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.394</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.697</v>
+        <v>1.121</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.821</v>
+        <v>0.73</v>
       </c>
       <c r="AB42" t="n">
         <v>0.394</v>
@@ -7167,13 +7167,13 @@
         <v>0.694</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.667</v>
+        <v>1.556</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.139</v>
+        <v>2.028</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.886</v>
+        <v>0.767</v>
       </c>
       <c r="AB43" t="n">
         <v>0.583</v>
@@ -7332,13 +7332,13 @@
         <v>0.105</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.711</v>
+        <v>0.421</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.842</v>
+        <v>0.553</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.844</v>
+        <v>0.762</v>
       </c>
       <c r="AB44" t="n">
         <v>0.184</v>
@@ -7359,22 +7359,22 @@
         <v>0.4</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.263</v>
+        <v>0.289</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.842</v>
+        <v>0.921</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.312</v>
+        <v>0.314</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.632</v>
+        <v>0.605</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.158</v>
+        <v>2.079</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.293</v>
+        <v>0.291</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
@@ -7497,13 +7497,13 @@
         <v>0.868</v>
       </c>
       <c r="Y45" t="n">
-        <v>6.553</v>
+        <v>4.684</v>
       </c>
       <c r="Z45" t="n">
-        <v>7.789</v>
+        <v>5.921</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.841</v>
+        <v>0.791</v>
       </c>
       <c r="AB45" t="n">
         <v>1</v>
@@ -7662,10 +7662,10 @@
         <v>0.16</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.6</v>
+        <v>0.04</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.6</v>
+        <v>0.04</v>
       </c>
       <c r="AA46" t="n">
         <v>1</v>
@@ -7827,13 +7827,13 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.947</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.158</v>
+        <v>0.895</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="AB47" t="n">
         <v>0.263</v>
@@ -8157,13 +8157,13 @@
         <v>5.342</v>
       </c>
       <c r="Y49" t="n">
-        <v>27.763</v>
+        <v>13.447</v>
       </c>
       <c r="Z49" t="n">
-        <v>31.947</v>
+        <v>17.632</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.869</v>
+        <v>0.763</v>
       </c>
       <c r="AB49" t="n">
         <v>7.816</v>
@@ -8184,22 +8184,22 @@
         <v>0.514</v>
       </c>
       <c r="AH49" t="n">
-        <v>1</v>
+        <v>1.158</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.342</v>
+        <v>2.711</v>
       </c>
       <c r="AJ49" t="n">
         <v>0.427</v>
       </c>
       <c r="AK49" t="n">
-        <v>8.132</v>
+        <v>7.974</v>
       </c>
       <c r="AL49" t="n">
-        <v>22.158</v>
+        <v>21.789</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
@@ -8322,13 +8322,13 @@
         <v>5.211</v>
       </c>
       <c r="Y50" t="n">
-        <v>27.632</v>
+        <v>12.974</v>
       </c>
       <c r="Z50" t="n">
-        <v>32.184</v>
+        <v>17.526</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.859</v>
+        <v>0.74</v>
       </c>
       <c r="AB50" t="n">
         <v>8.157999999999999</v>
@@ -8349,22 +8349,22 @@
         <v>0.318</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.711</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.263</v>
+        <v>2.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.314</v>
+        <v>0.326</v>
       </c>
       <c r="AK50" t="n">
-        <v>8.026</v>
+        <v>7.921</v>
       </c>
       <c r="AL50" t="n">
-        <v>24.105</v>
+        <v>23.868</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
